--- a/output/pdf_financials_xlsx/MAI.xlsx
+++ b/output/pdf_financials_xlsx/MAI.xlsx
@@ -6390,10 +6390,10 @@
         <v>3.711913</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>3.711913</v>
+        <v>3.870353</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>3.711913</v>
+        <v>3.983078</v>
       </c>
       <c r="O92" s="3" t="n">
         <v>3.711913</v>
@@ -28116,7 +28116,11 @@
           <t>Warrants reserve 13</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MAI.xlsx
+++ b/output/pdf_financials_xlsx/MAI.xlsx
@@ -1137,16 +1137,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000124</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003094</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004789</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.009639</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -2234,16 +2234,16 @@
         <v>0.03404</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.138659</v>
+        <v>-1.138535</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.56607</v>
+        <v>-1.562976</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-5.799863</v>
+        <v>-5.795074</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-6.262333</v>
+        <v>-6.252694</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-25.619799</v>
@@ -2368,16 +2368,16 @@
         <v>0.039781</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.133437</v>
+        <v>-1.133313</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.560887</v>
+        <v>-1.557793</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-5.793984</v>
+        <v>-5.789195</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-6.252216</v>
+        <v>-6.242577</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-25.592245</v>
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.306806</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.208494</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.208494</v>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.306806</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.208494</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.208494</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.45763</v>
+        <v>0.150824</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.245344</v>
+        <v>0.03685</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.03685</v>
@@ -3579,10 +3579,10 @@
         <v>13.812975</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>4.557</v>
+        <v>4.314409</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>6.307</v>
+        <v>6.376</v>
       </c>
     </row>
     <row r="49">
@@ -8312,25 +8312,25 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.113282</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.113465</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.110183</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.101864</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.109536</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>0</v>
+        <v>-0.111</v>
       </c>
     </row>
     <row r="125">
@@ -8373,25 +8373,25 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.113282</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.113465</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.110183</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.101864</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>6.928</v>
+        <v>6.818464</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0</v>
+        <v>-0.111</v>
       </c>
     </row>
     <row r="126">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -46528,7 +46528,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E357" s="5" t="n">
@@ -50928,7 +50928,11 @@
           <t>Lease payments 18</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -53580,7 +53584,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
           <t>-</t>
@@ -56340,7 +56348,11 @@
           <t>Lease payments 10</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
           <t>-</t>
@@ -82266,7 +82278,7 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
@@ -84866,7 +84878,7 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
@@ -85602,7 +85614,7 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
@@ -86444,7 +86456,11 @@
           <t>Interest expense 16.</t>
         </is>
       </c>
-      <c r="D738" t="inlineStr"/>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E738" t="inlineStr">
         <is>
           <t>-</t>
@@ -87186,7 +87202,7 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
@@ -89368,7 +89384,7 @@
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">

--- a/output/pdf_financials_xlsx/MAI.xlsx
+++ b/output/pdf_financials_xlsx/MAI.xlsx
@@ -6111,10 +6111,10 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>28.783076</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>29.589571</v>
       </c>
       <c r="D88" s="3" t="n">
         <v>29.013403</v>
@@ -47484,7 +47484,11 @@
           <t>Share capital, note 7</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E366" s="5" t="n">
         <v>28.783076</v>
       </c>
